--- a/frontend/public/product-template.xlsx
+++ b/frontend/public/product-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\shop-management-system\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18234721-57DA-4E52-B982-BDC4D544FF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE50A0A3-F53A-4B56-A6E2-9D697CFB6D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{49DA3F26-1DD6-4CC9-AA22-FD2A2F567E53}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>name</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>packName</t>
+  </si>
+  <si>
+    <t>category</t>
   </si>
 </sst>
 </file>
@@ -418,45 +421,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D081A662-C358-48BA-AD69-D3A4889395DD}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/frontend/public/product-template.xlsx
+++ b/frontend/public/product-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\shop-management-system\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE50A0A3-F53A-4B56-A6E2-9D697CFB6D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565B1FA9-7E88-453D-A897-E07516BF5DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{49DA3F26-1DD6-4CC9-AA22-FD2A2F567E53}"/>
+    <workbookView xWindow="0" yWindow="1500" windowWidth="28800" windowHeight="14700" xr2:uid="{49DA3F26-1DD6-4CC9-AA22-FD2A2F567E53}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>name</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>category</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>expiryDate</t>
   </si>
 </sst>
 </file>
@@ -421,17 +427,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D081A662-C358-48BA-AD69-D3A4889395DD}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,30 +446,36 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
     </row>
